--- a/event_feedback_forms/017_promoter_daily_activity_report--event_feedback_forms.xlsx
+++ b/event_feedback_forms/017_promoter_daily_activity_report--event_feedback_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,13 +437,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E27"/>
+  <dimension ref="A1:E16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
     <col width="19" customWidth="1" min="2" max="2"/>
     <col width="19" customWidth="1" min="3" max="3"/>
-    <col width="21" customWidth="1" min="4" max="4"/>
+    <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -538,23 +538,23 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>event_id</t>
+          <t>event_type</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Event Id</t>
+          <t>Event Type</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -566,92 +566,84 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>event_type</t>
+          <t>activity_type</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Event Type</t>
+          <t>Activity Type</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>event_name</t>
+          <t>activity_location</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Event Name</t>
+          <t>Activity Location</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>start_time</t>
+          <t>activity_details</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Start Time</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>24 hour time format</t>
-        </is>
-      </c>
+          <t>Activity Details</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>end_time</t>
+          <t>activity_duration</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>End Time</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>24 hour time format</t>
-        </is>
-      </c>
+          <t>Activity Duration</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
           <t>no</t>
@@ -661,23 +653,23 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>activity_type</t>
+          <t>promoter_team</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Activity Type</t>
+          <t>Promoter Team</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -689,18 +681,18 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>activity_details</t>
+          <t>email</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Activity Details</t>
+          <t>Email</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -712,12 +704,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>activity_duration</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Activity Duration</t>
+          <t>Phone</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -730,46 +722,46 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>activity_location</t>
+          <t>event_id</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Activity Location</t>
+          <t>Event ID</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>promoter_team</t>
+          <t>event_notes</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Promoter Team</t>
+          <t>Event Notes</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -781,12 +773,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>promoter_notes</t>
+          <t>notes</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Promoter Notes</t>
+          <t>Notes</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -799,274 +791,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>event_notes</t>
+          <t>event_id_2</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Event Notes</t>
+          <t>Event ID 2</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>email</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Email</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>phone</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Phone</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>event_id_2</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Event Id</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>event_id_3</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Event Id</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>event_id_4</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Event Id</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>event_id_5</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Event Id</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>event_id_6</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Event Id</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>event_id_7</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Event Id</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>event_id_8</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Event Id</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>event_id_9</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Event Id</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>event_id_10</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Event Id</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1087,8 +826,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="27" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1116,12 +855,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'event',_'value':_'event'}</t>
+          <t>event</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Event', 'value': 'Event'}</t>
+          <t>Event</t>
         </is>
       </c>
     </row>
@@ -1133,12 +872,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'non_event',_'value':_'non_event'}</t>
+          <t>non_event</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Non Event', 'value': 'Non Event'}</t>
+          <t>Non Event</t>
         </is>
       </c>
     </row>
@@ -1150,12 +889,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'on-site',_'value':_'on-site'}</t>
+          <t>on-site</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'On-Site', 'value': 'On-Site'}</t>
+          <t>On-Site</t>
         </is>
       </c>
     </row>
@@ -1167,12 +906,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'off-site',_'value':_'off-site'}</t>
+          <t>off-site</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Off-Site', 'value': 'Off-Site'}</t>
+          <t>Off-Site</t>
         </is>
       </c>
     </row>
@@ -1184,12 +923,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'hybrid',_'value':_'hybrid'}</t>
+          <t>hybrid</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Hybrid', 'value': 'Hybrid'}</t>
+          <t>Hybrid</t>
         </is>
       </c>
     </row>
@@ -1201,12 +940,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'on-site',_'value':_'on-site'}</t>
+          <t>on-site</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'On-Site', 'value': 'On-Site'}</t>
+          <t>On-Site</t>
         </is>
       </c>
     </row>
@@ -1218,12 +957,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'off-site',_'value':_'off-site'}</t>
+          <t>off-site</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Off-Site', 'value': 'Off-Site'}</t>
+          <t>Off-Site</t>
         </is>
       </c>
     </row>
@@ -1235,12 +974,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'hybrid',_'value':_'hybrid'}</t>
+          <t>hybrid</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Hybrid', 'value': 'Hybrid'}</t>
+          <t>Hybrid</t>
         </is>
       </c>
     </row>
@@ -1252,12 +991,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'other',_'value':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Other', 'value': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1269,12 +1008,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_5,_'label':_'unknown',_'value':_'unknown'}</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 5, 'label': 'Unknown', 'value': 'Unknown'}</t>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
